--- a/artfynd/A 54905-2024 artfynd.xlsx
+++ b/artfynd/A 54905-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>121283100</v>
+        <v>121283095</v>
       </c>
       <c r="B2" t="n">
-        <v>91963</v>
+        <v>91973</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>691921</v>
+        <v>691922</v>
       </c>
       <c r="R2" t="n">
-        <v>7138415</v>
+        <v>7138424</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -781,10 +781,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>121283095</v>
+        <v>121283098</v>
       </c>
       <c r="B3" t="n">
-        <v>91963</v>
+        <v>78601</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -793,25 +793,25 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>4364</v>
+        <v>6425</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -821,10 +821,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>691922</v>
+        <v>691902</v>
       </c>
       <c r="R3" t="n">
-        <v>7138424</v>
+        <v>7138371</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -887,10 +887,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>121283098</v>
+        <v>121283100</v>
       </c>
       <c r="B4" t="n">
-        <v>78598</v>
+        <v>91973</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -899,25 +899,25 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6425</v>
+        <v>4364</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -927,10 +927,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>691902</v>
+        <v>691921</v>
       </c>
       <c r="R4" t="n">
-        <v>7138371</v>
+        <v>7138415</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>

--- a/artfynd/A 54905-2024 artfynd.xlsx
+++ b/artfynd/A 54905-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>121283095</v>
+        <v>121283100</v>
       </c>
       <c r="B2" t="n">
-        <v>91973</v>
+        <v>91985</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>691922</v>
+        <v>691921</v>
       </c>
       <c r="R2" t="n">
-        <v>7138424</v>
+        <v>7138415</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -784,7 +784,7 @@
         <v>121283098</v>
       </c>
       <c r="B3" t="n">
-        <v>78601</v>
+        <v>78604</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -887,10 +887,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>121283100</v>
+        <v>121283095</v>
       </c>
       <c r="B4" t="n">
-        <v>91973</v>
+        <v>91985</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -927,10 +927,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>691921</v>
+        <v>691922</v>
       </c>
       <c r="R4" t="n">
-        <v>7138415</v>
+        <v>7138424</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>

--- a/artfynd/A 54905-2024 artfynd.xlsx
+++ b/artfynd/A 54905-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>121283100</v>
+        <v>121283095</v>
       </c>
       <c r="B2" t="n">
-        <v>91985</v>
+        <v>91986</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>691921</v>
+        <v>691922</v>
       </c>
       <c r="R2" t="n">
-        <v>7138415</v>
+        <v>7138424</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -887,10 +887,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>121283095</v>
+        <v>121283100</v>
       </c>
       <c r="B4" t="n">
-        <v>91985</v>
+        <v>91986</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -927,10 +927,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>691922</v>
+        <v>691921</v>
       </c>
       <c r="R4" t="n">
-        <v>7138424</v>
+        <v>7138415</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>

--- a/artfynd/A 54905-2024 artfynd.xlsx
+++ b/artfynd/A 54905-2024 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>121283095</v>
       </c>
       <c r="B2" t="n">
-        <v>91986</v>
+        <v>91989</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -784,7 +784,7 @@
         <v>121283098</v>
       </c>
       <c r="B3" t="n">
-        <v>78604</v>
+        <v>78607</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -890,7 +890,7 @@
         <v>121283100</v>
       </c>
       <c r="B4" t="n">
-        <v>91986</v>
+        <v>91989</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>

--- a/artfynd/A 54905-2024 artfynd.xlsx
+++ b/artfynd/A 54905-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>121283095</v>
+        <v>121283098</v>
       </c>
       <c r="B2" t="n">
-        <v>91989</v>
+        <v>78607</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,25 +687,25 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>4364</v>
+        <v>6425</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>691922</v>
+        <v>691902</v>
       </c>
       <c r="R2" t="n">
-        <v>7138424</v>
+        <v>7138371</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -781,10 +781,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>121283098</v>
+        <v>121283100</v>
       </c>
       <c r="B3" t="n">
-        <v>78607</v>
+        <v>91989</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -793,25 +793,25 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6425</v>
+        <v>4364</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -821,10 +821,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>691902</v>
+        <v>691921</v>
       </c>
       <c r="R3" t="n">
-        <v>7138371</v>
+        <v>7138415</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -887,7 +887,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>121283100</v>
+        <v>121283095</v>
       </c>
       <c r="B4" t="n">
         <v>91989</v>
@@ -927,10 +927,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>691921</v>
+        <v>691922</v>
       </c>
       <c r="R4" t="n">
-        <v>7138415</v>
+        <v>7138424</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>

--- a/artfynd/A 54905-2024 artfynd.xlsx
+++ b/artfynd/A 54905-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>121283098</v>
+        <v>121283095</v>
       </c>
       <c r="B2" t="n">
-        <v>78607</v>
+        <v>91995</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,25 +687,25 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6425</v>
+        <v>4364</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>691902</v>
+        <v>691922</v>
       </c>
       <c r="R2" t="n">
-        <v>7138371</v>
+        <v>7138424</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -784,7 +784,7 @@
         <v>121283100</v>
       </c>
       <c r="B3" t="n">
-        <v>91989</v>
+        <v>91995</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -887,10 +887,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>121283095</v>
+        <v>121283098</v>
       </c>
       <c r="B4" t="n">
-        <v>91989</v>
+        <v>78608</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -899,25 +899,25 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>4364</v>
+        <v>6425</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -927,10 +927,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>691922</v>
+        <v>691902</v>
       </c>
       <c r="R4" t="n">
-        <v>7138424</v>
+        <v>7138371</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>

--- a/artfynd/A 54905-2024 artfynd.xlsx
+++ b/artfynd/A 54905-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>121283095</v>
+        <v>121283100</v>
       </c>
       <c r="B2" t="n">
-        <v>91995</v>
+        <v>91996</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>691922</v>
+        <v>691921</v>
       </c>
       <c r="R2" t="n">
-        <v>7138424</v>
+        <v>7138415</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -781,10 +781,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>121283100</v>
+        <v>121283095</v>
       </c>
       <c r="B3" t="n">
-        <v>91995</v>
+        <v>91996</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -821,10 +821,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>691921</v>
+        <v>691922</v>
       </c>
       <c r="R3" t="n">
-        <v>7138415</v>
+        <v>7138424</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -890,7 +890,7 @@
         <v>121283098</v>
       </c>
       <c r="B4" t="n">
-        <v>78608</v>
+        <v>78609</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>

--- a/artfynd/A 54905-2024 artfynd.xlsx
+++ b/artfynd/A 54905-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>121283100</v>
+        <v>121283098</v>
       </c>
       <c r="B2" t="n">
-        <v>91996</v>
+        <v>78609</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,25 +687,25 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>4364</v>
+        <v>6425</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>691921</v>
+        <v>691902</v>
       </c>
       <c r="R2" t="n">
-        <v>7138415</v>
+        <v>7138371</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -781,7 +781,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>121283095</v>
+        <v>121283100</v>
       </c>
       <c r="B3" t="n">
         <v>91996</v>
@@ -821,10 +821,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>691922</v>
+        <v>691921</v>
       </c>
       <c r="R3" t="n">
-        <v>7138424</v>
+        <v>7138415</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -887,10 +887,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>121283098</v>
+        <v>121283095</v>
       </c>
       <c r="B4" t="n">
-        <v>78609</v>
+        <v>91996</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -899,25 +899,25 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6425</v>
+        <v>4364</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -927,10 +927,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>691902</v>
+        <v>691922</v>
       </c>
       <c r="R4" t="n">
-        <v>7138371</v>
+        <v>7138424</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>

--- a/artfynd/A 54905-2024 artfynd.xlsx
+++ b/artfynd/A 54905-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>121283098</v>
+        <v>121283100</v>
       </c>
       <c r="B2" t="n">
-        <v>78609</v>
+        <v>91996</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,25 +687,25 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6425</v>
+        <v>4364</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>691902</v>
+        <v>691921</v>
       </c>
       <c r="R2" t="n">
-        <v>7138371</v>
+        <v>7138415</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -781,7 +781,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>121283100</v>
+        <v>121283095</v>
       </c>
       <c r="B3" t="n">
         <v>91996</v>
@@ -821,10 +821,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>691921</v>
+        <v>691922</v>
       </c>
       <c r="R3" t="n">
-        <v>7138415</v>
+        <v>7138424</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -887,10 +887,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>121283095</v>
+        <v>121283098</v>
       </c>
       <c r="B4" t="n">
-        <v>91996</v>
+        <v>78609</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -899,25 +899,25 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>4364</v>
+        <v>6425</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -927,10 +927,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>691922</v>
+        <v>691902</v>
       </c>
       <c r="R4" t="n">
-        <v>7138424</v>
+        <v>7138371</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>

--- a/artfynd/A 54905-2024 artfynd.xlsx
+++ b/artfynd/A 54905-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>121283100</v>
+        <v>121283095</v>
       </c>
       <c r="B2" t="n">
-        <v>91996</v>
+        <v>92001</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>691921</v>
+        <v>691922</v>
       </c>
       <c r="R2" t="n">
-        <v>7138415</v>
+        <v>7138424</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -781,10 +781,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>121283095</v>
+        <v>121283098</v>
       </c>
       <c r="B3" t="n">
-        <v>91996</v>
+        <v>78614</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -793,25 +793,25 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>4364</v>
+        <v>6425</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -821,10 +821,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>691922</v>
+        <v>691902</v>
       </c>
       <c r="R3" t="n">
-        <v>7138424</v>
+        <v>7138371</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -887,10 +887,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>121283098</v>
+        <v>121283100</v>
       </c>
       <c r="B4" t="n">
-        <v>78609</v>
+        <v>92001</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -899,25 +899,25 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6425</v>
+        <v>4364</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -927,10 +927,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>691902</v>
+        <v>691921</v>
       </c>
       <c r="R4" t="n">
-        <v>7138371</v>
+        <v>7138415</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>

--- a/artfynd/A 54905-2024 artfynd.xlsx
+++ b/artfynd/A 54905-2024 artfynd.xlsx
@@ -1104,10 +1104,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>122031430</v>
+        <v>122031256</v>
       </c>
       <c r="B6" t="n">
-        <v>91026</v>
+        <v>92055</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1116,25 +1116,25 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>65</v>
+        <v>4364</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Fläckporing</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Anthoporia albobrunnea</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Romell) Karasiński &amp; Niemelä</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
@@ -1148,10 +1148,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>691925</v>
+        <v>691950</v>
       </c>
       <c r="R6" t="n">
-        <v>7138401</v>
+        <v>7138360</v>
       </c>
       <c r="S6" t="n">
         <v>5</v>
@@ -1178,12 +1178,12 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2024-11-22</t>
+          <t>2024-11-12</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>2024-11-22</t>
+          <t>2024-11-12</t>
         </is>
       </c>
       <c r="AC6" t="inlineStr">
@@ -1215,10 +1215,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>122031768</v>
+        <v>122031483</v>
       </c>
       <c r="B7" t="n">
-        <v>78381</v>
+        <v>92055</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1227,25 +1227,25 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6446</v>
+        <v>4364</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
@@ -1259,10 +1259,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>691878</v>
+        <v>691930</v>
       </c>
       <c r="R7" t="n">
-        <v>7138386</v>
+        <v>7138353</v>
       </c>
       <c r="S7" t="n">
         <v>5</v>
@@ -1326,10 +1326,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>122031256</v>
+        <v>122031257</v>
       </c>
       <c r="B8" t="n">
-        <v>92055</v>
+        <v>91026</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1338,25 +1338,25 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>4364</v>
+        <v>65</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Fläckporing</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Anthoporia albobrunnea</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Romell) Karasiński &amp; Niemelä</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
@@ -1370,10 +1370,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>691950</v>
+        <v>691922</v>
       </c>
       <c r="R8" t="n">
-        <v>7138360</v>
+        <v>7138420</v>
       </c>
       <c r="S8" t="n">
         <v>5</v>
@@ -1437,10 +1437,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>122031483</v>
+        <v>122031430</v>
       </c>
       <c r="B9" t="n">
-        <v>92055</v>
+        <v>91026</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1449,25 +1449,25 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>4364</v>
+        <v>65</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Fläckporing</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Anthoporia albobrunnea</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Romell) Karasiński &amp; Niemelä</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
@@ -1481,10 +1481,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>691930</v>
+        <v>691925</v>
       </c>
       <c r="R9" t="n">
-        <v>7138353</v>
+        <v>7138401</v>
       </c>
       <c r="S9" t="n">
         <v>5</v>
@@ -1548,10 +1548,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>122031257</v>
+        <v>122031768</v>
       </c>
       <c r="B10" t="n">
-        <v>91026</v>
+        <v>78381</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1560,25 +1560,25 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>65</v>
+        <v>6446</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Fläckporing</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Anthoporia albobrunnea</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Romell) Karasiński &amp; Niemelä</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
@@ -1592,10 +1592,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>691922</v>
+        <v>691878</v>
       </c>
       <c r="R10" t="n">
-        <v>7138420</v>
+        <v>7138386</v>
       </c>
       <c r="S10" t="n">
         <v>5</v>
@@ -1622,12 +1622,12 @@
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>2024-11-12</t>
+          <t>2024-11-22</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>2024-11-12</t>
+          <t>2024-11-22</t>
         </is>
       </c>
       <c r="AC10" t="inlineStr">

--- a/artfynd/A 54905-2024 artfynd.xlsx
+++ b/artfynd/A 54905-2024 artfynd.xlsx
@@ -993,10 +993,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>122031255</v>
+        <v>122031768</v>
       </c>
       <c r="B5" t="n">
-        <v>78381</v>
+        <v>78382</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1037,10 +1037,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>691884</v>
+        <v>691878</v>
       </c>
       <c r="R5" t="n">
-        <v>7138400</v>
+        <v>7138386</v>
       </c>
       <c r="S5" t="n">
         <v>5</v>
@@ -1067,12 +1067,12 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2024-11-12</t>
+          <t>2024-11-22</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2024-11-12</t>
+          <t>2024-11-22</t>
         </is>
       </c>
       <c r="AC5" t="inlineStr">
@@ -1104,10 +1104,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>122031256</v>
+        <v>122031255</v>
       </c>
       <c r="B6" t="n">
-        <v>92055</v>
+        <v>78382</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1116,25 +1116,25 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>4364</v>
+        <v>6446</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
@@ -1148,10 +1148,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>691950</v>
+        <v>691884</v>
       </c>
       <c r="R6" t="n">
-        <v>7138360</v>
+        <v>7138400</v>
       </c>
       <c r="S6" t="n">
         <v>5</v>
@@ -1215,10 +1215,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>122031483</v>
+        <v>122031257</v>
       </c>
       <c r="B7" t="n">
-        <v>92055</v>
+        <v>91036</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1227,25 +1227,25 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>4364</v>
+        <v>65</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Fläckporing</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Anthoporia albobrunnea</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Romell) Karasiński &amp; Niemelä</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
@@ -1259,10 +1259,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>691930</v>
+        <v>691922</v>
       </c>
       <c r="R7" t="n">
-        <v>7138353</v>
+        <v>7138420</v>
       </c>
       <c r="S7" t="n">
         <v>5</v>
@@ -1289,12 +1289,12 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2024-11-22</t>
+          <t>2024-11-12</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>2024-11-22</t>
+          <t>2024-11-12</t>
         </is>
       </c>
       <c r="AC7" t="inlineStr">
@@ -1326,10 +1326,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>122031257</v>
+        <v>122031483</v>
       </c>
       <c r="B8" t="n">
-        <v>91026</v>
+        <v>92065</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1338,25 +1338,25 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>65</v>
+        <v>4364</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Fläckporing</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Anthoporia albobrunnea</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Romell) Karasiński &amp; Niemelä</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
@@ -1370,10 +1370,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>691922</v>
+        <v>691930</v>
       </c>
       <c r="R8" t="n">
-        <v>7138420</v>
+        <v>7138353</v>
       </c>
       <c r="S8" t="n">
         <v>5</v>
@@ -1400,12 +1400,12 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2024-11-12</t>
+          <t>2024-11-22</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>2024-11-12</t>
+          <t>2024-11-22</t>
         </is>
       </c>
       <c r="AC8" t="inlineStr">
@@ -1437,10 +1437,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>122031430</v>
+        <v>122031256</v>
       </c>
       <c r="B9" t="n">
-        <v>91026</v>
+        <v>92065</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1449,25 +1449,25 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>65</v>
+        <v>4364</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Fläckporing</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Anthoporia albobrunnea</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Romell) Karasiński &amp; Niemelä</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
@@ -1481,10 +1481,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>691925</v>
+        <v>691950</v>
       </c>
       <c r="R9" t="n">
-        <v>7138401</v>
+        <v>7138360</v>
       </c>
       <c r="S9" t="n">
         <v>5</v>
@@ -1511,12 +1511,12 @@
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>2024-11-22</t>
+          <t>2024-11-12</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>2024-11-22</t>
+          <t>2024-11-12</t>
         </is>
       </c>
       <c r="AC9" t="inlineStr">
@@ -1548,10 +1548,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>122031768</v>
+        <v>122031430</v>
       </c>
       <c r="B10" t="n">
-        <v>78381</v>
+        <v>91036</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1560,25 +1560,25 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6446</v>
+        <v>65</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Fläckporing</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Anthoporia albobrunnea</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Romell) Karasiński &amp; Niemelä</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
@@ -1592,10 +1592,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>691878</v>
+        <v>691925</v>
       </c>
       <c r="R10" t="n">
-        <v>7138386</v>
+        <v>7138401</v>
       </c>
       <c r="S10" t="n">
         <v>5</v>

--- a/artfynd/A 54905-2024 artfynd.xlsx
+++ b/artfynd/A 54905-2024 artfynd.xlsx
@@ -993,10 +993,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>122031768</v>
+        <v>122031256</v>
       </c>
       <c r="B5" t="n">
-        <v>78382</v>
+        <v>92065</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1005,25 +1005,25 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6446</v>
+        <v>4364</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
@@ -1037,10 +1037,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>691878</v>
+        <v>691950</v>
       </c>
       <c r="R5" t="n">
-        <v>7138386</v>
+        <v>7138360</v>
       </c>
       <c r="S5" t="n">
         <v>5</v>
@@ -1067,12 +1067,12 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2024-11-22</t>
+          <t>2024-11-12</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2024-11-22</t>
+          <t>2024-11-12</t>
         </is>
       </c>
       <c r="AC5" t="inlineStr">
@@ -1326,10 +1326,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>122031483</v>
+        <v>122031768</v>
       </c>
       <c r="B8" t="n">
-        <v>92065</v>
+        <v>78382</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1338,25 +1338,25 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>4364</v>
+        <v>6446</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
@@ -1370,10 +1370,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>691930</v>
+        <v>691878</v>
       </c>
       <c r="R8" t="n">
-        <v>7138353</v>
+        <v>7138386</v>
       </c>
       <c r="S8" t="n">
         <v>5</v>
@@ -1437,7 +1437,7 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>122031256</v>
+        <v>122031483</v>
       </c>
       <c r="B9" t="n">
         <v>92065</v>
@@ -1481,10 +1481,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>691950</v>
+        <v>691930</v>
       </c>
       <c r="R9" t="n">
-        <v>7138360</v>
+        <v>7138353</v>
       </c>
       <c r="S9" t="n">
         <v>5</v>
@@ -1511,12 +1511,12 @@
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>2024-11-12</t>
+          <t>2024-11-22</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>2024-11-12</t>
+          <t>2024-11-22</t>
         </is>
       </c>
       <c r="AC9" t="inlineStr">

--- a/artfynd/A 54905-2024 artfynd.xlsx
+++ b/artfynd/A 54905-2024 artfynd.xlsx
@@ -993,10 +993,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>122031256</v>
+        <v>122031257</v>
       </c>
       <c r="B5" t="n">
-        <v>92065</v>
+        <v>91048</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1005,25 +1005,25 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>4364</v>
+        <v>65</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Fläckporing</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Anthoporia albobrunnea</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Romell) Karasiński &amp; Niemelä</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
@@ -1037,10 +1037,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>691950</v>
+        <v>691922</v>
       </c>
       <c r="R5" t="n">
-        <v>7138360</v>
+        <v>7138420</v>
       </c>
       <c r="S5" t="n">
         <v>5</v>
@@ -1104,10 +1104,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>122031255</v>
+        <v>122031768</v>
       </c>
       <c r="B6" t="n">
-        <v>78382</v>
+        <v>78387</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1148,10 +1148,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>691884</v>
+        <v>691878</v>
       </c>
       <c r="R6" t="n">
-        <v>7138400</v>
+        <v>7138386</v>
       </c>
       <c r="S6" t="n">
         <v>5</v>
@@ -1178,12 +1178,12 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2024-11-12</t>
+          <t>2024-11-22</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>2024-11-12</t>
+          <t>2024-11-22</t>
         </is>
       </c>
       <c r="AC6" t="inlineStr">
@@ -1215,10 +1215,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>122031257</v>
+        <v>122031483</v>
       </c>
       <c r="B7" t="n">
-        <v>91036</v>
+        <v>92077</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1227,25 +1227,25 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>65</v>
+        <v>4364</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Fläckporing</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Anthoporia albobrunnea</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Romell) Karasiński &amp; Niemelä</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
@@ -1259,10 +1259,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>691922</v>
+        <v>691930</v>
       </c>
       <c r="R7" t="n">
-        <v>7138420</v>
+        <v>7138353</v>
       </c>
       <c r="S7" t="n">
         <v>5</v>
@@ -1289,12 +1289,12 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2024-11-12</t>
+          <t>2024-11-22</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>2024-11-12</t>
+          <t>2024-11-22</t>
         </is>
       </c>
       <c r="AC7" t="inlineStr">
@@ -1326,10 +1326,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>122031768</v>
+        <v>122031256</v>
       </c>
       <c r="B8" t="n">
-        <v>78382</v>
+        <v>92077</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1338,25 +1338,25 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6446</v>
+        <v>4364</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
@@ -1370,10 +1370,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>691878</v>
+        <v>691950</v>
       </c>
       <c r="R8" t="n">
-        <v>7138386</v>
+        <v>7138360</v>
       </c>
       <c r="S8" t="n">
         <v>5</v>
@@ -1400,12 +1400,12 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2024-11-22</t>
+          <t>2024-11-12</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>2024-11-22</t>
+          <t>2024-11-12</t>
         </is>
       </c>
       <c r="AC8" t="inlineStr">
@@ -1437,10 +1437,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>122031483</v>
+        <v>122031430</v>
       </c>
       <c r="B9" t="n">
-        <v>92065</v>
+        <v>91048</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1449,25 +1449,25 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>4364</v>
+        <v>65</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Fläckporing</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Anthoporia albobrunnea</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Romell) Karasiński &amp; Niemelä</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
@@ -1481,10 +1481,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>691930</v>
+        <v>691925</v>
       </c>
       <c r="R9" t="n">
-        <v>7138353</v>
+        <v>7138401</v>
       </c>
       <c r="S9" t="n">
         <v>5</v>
@@ -1548,10 +1548,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>122031430</v>
+        <v>122031255</v>
       </c>
       <c r="B10" t="n">
-        <v>91036</v>
+        <v>78387</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1560,25 +1560,25 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>65</v>
+        <v>6446</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Fläckporing</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Anthoporia albobrunnea</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Romell) Karasiński &amp; Niemelä</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
@@ -1592,10 +1592,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>691925</v>
+        <v>691884</v>
       </c>
       <c r="R10" t="n">
-        <v>7138401</v>
+        <v>7138400</v>
       </c>
       <c r="S10" t="n">
         <v>5</v>
@@ -1622,12 +1622,12 @@
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>2024-11-22</t>
+          <t>2024-11-12</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>2024-11-22</t>
+          <t>2024-11-12</t>
         </is>
       </c>
       <c r="AC10" t="inlineStr">

--- a/artfynd/A 54905-2024 artfynd.xlsx
+++ b/artfynd/A 54905-2024 artfynd.xlsx
@@ -993,10 +993,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>122031257</v>
+        <v>122031483</v>
       </c>
       <c r="B5" t="n">
-        <v>91048</v>
+        <v>92082</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1005,25 +1005,25 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>65</v>
+        <v>4364</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Fläckporing</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Anthoporia albobrunnea</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Romell) Karasiński &amp; Niemelä</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
@@ -1037,10 +1037,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>691922</v>
+        <v>691930</v>
       </c>
       <c r="R5" t="n">
-        <v>7138420</v>
+        <v>7138353</v>
       </c>
       <c r="S5" t="n">
         <v>5</v>
@@ -1067,12 +1067,12 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2024-11-12</t>
+          <t>2024-11-22</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2024-11-12</t>
+          <t>2024-11-22</t>
         </is>
       </c>
       <c r="AC5" t="inlineStr">
@@ -1104,10 +1104,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>122031768</v>
+        <v>122031256</v>
       </c>
       <c r="B6" t="n">
-        <v>78387</v>
+        <v>92082</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1116,25 +1116,25 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6446</v>
+        <v>4364</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
@@ -1148,10 +1148,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>691878</v>
+        <v>691950</v>
       </c>
       <c r="R6" t="n">
-        <v>7138386</v>
+        <v>7138360</v>
       </c>
       <c r="S6" t="n">
         <v>5</v>
@@ -1178,12 +1178,12 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2024-11-22</t>
+          <t>2024-11-12</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>2024-11-22</t>
+          <t>2024-11-12</t>
         </is>
       </c>
       <c r="AC6" t="inlineStr">
@@ -1215,10 +1215,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>122031483</v>
+        <v>122031257</v>
       </c>
       <c r="B7" t="n">
-        <v>92077</v>
+        <v>91053</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1227,25 +1227,25 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>4364</v>
+        <v>65</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Fläckporing</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Anthoporia albobrunnea</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Romell) Karasiński &amp; Niemelä</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
@@ -1259,10 +1259,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>691930</v>
+        <v>691922</v>
       </c>
       <c r="R7" t="n">
-        <v>7138353</v>
+        <v>7138420</v>
       </c>
       <c r="S7" t="n">
         <v>5</v>
@@ -1289,12 +1289,12 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2024-11-22</t>
+          <t>2024-11-12</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>2024-11-22</t>
+          <t>2024-11-12</t>
         </is>
       </c>
       <c r="AC7" t="inlineStr">
@@ -1326,10 +1326,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>122031256</v>
+        <v>122031430</v>
       </c>
       <c r="B8" t="n">
-        <v>92077</v>
+        <v>91053</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1338,25 +1338,25 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>4364</v>
+        <v>65</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Fläckporing</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Anthoporia albobrunnea</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Romell) Karasiński &amp; Niemelä</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
@@ -1370,10 +1370,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>691950</v>
+        <v>691925</v>
       </c>
       <c r="R8" t="n">
-        <v>7138360</v>
+        <v>7138401</v>
       </c>
       <c r="S8" t="n">
         <v>5</v>
@@ -1400,12 +1400,12 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2024-11-12</t>
+          <t>2024-11-22</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>2024-11-12</t>
+          <t>2024-11-22</t>
         </is>
       </c>
       <c r="AC8" t="inlineStr">
@@ -1437,10 +1437,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>122031430</v>
+        <v>122031768</v>
       </c>
       <c r="B9" t="n">
-        <v>91048</v>
+        <v>78387</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1449,25 +1449,25 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>65</v>
+        <v>6446</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Fläckporing</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Anthoporia albobrunnea</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Romell) Karasiński &amp; Niemelä</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
@@ -1481,10 +1481,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>691925</v>
+        <v>691878</v>
       </c>
       <c r="R9" t="n">
-        <v>7138401</v>
+        <v>7138386</v>
       </c>
       <c r="S9" t="n">
         <v>5</v>

--- a/artfynd/A 54905-2024 artfynd.xlsx
+++ b/artfynd/A 54905-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY10"/>
+  <dimension ref="A1:AY11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,53 +675,52 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>121283095</v>
+        <v>122031257</v>
       </c>
       <c r="B2" t="n">
-        <v>92001</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92183</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>4364</v>
+        <v>65</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Fläckporing</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Anthoporia albobrunnea</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr"/>
+          <t>(Romell) Karasiński &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Vittanliden, Ly lm</t>
+          <t>Byssträsk, Ly lm</t>
         </is>
       </c>
       <c r="Q2" t="n">
         <v>691922</v>
       </c>
       <c r="R2" t="n">
-        <v>7138424</v>
+        <v>7138420</v>
       </c>
       <c r="S2" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -745,12 +744,17 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2024-08-28</t>
+          <t>2024-11-12</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2024-08-28</t>
+          <t>2024-11-12</t>
+        </is>
+      </c>
+      <c r="AC2" t="inlineStr">
+        <is>
+          <t>Påträffad under Sveaskogs naturvärdesinventering</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -765,69 +769,64 @@
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Elijah Ourth</t>
+          <t>Mimmi Persson</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Elijah Ourth</t>
-        </is>
-      </c>
-      <c r="AY2" t="inlineStr">
-        <is>
-          <t>Ecogain</t>
-        </is>
-      </c>
+          <t>Mimmi Persson</t>
+        </is>
+      </c>
+      <c r="AY2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>121283098</v>
+        <v>122031430</v>
       </c>
       <c r="B3" t="n">
-        <v>78614</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92183</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6425</v>
+        <v>65</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Fläckporing</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Anthoporia albobrunnea</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr"/>
+          <t>(Romell) Karasiński &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Vittanliden, Ly lm</t>
+          <t>Byssträsk, Ly lm</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>691902</v>
+        <v>691925</v>
       </c>
       <c r="R3" t="n">
-        <v>7138371</v>
+        <v>7138401</v>
       </c>
       <c r="S3" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -851,12 +850,17 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2024-08-28</t>
+          <t>2024-11-22</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2024-08-28</t>
+          <t>2024-11-22</t>
+        </is>
+      </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>Påträffad under Sveaskogs naturvärdesinventering</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -871,53 +875,44 @@
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Elijah Ourth</t>
+          <t>Mimmi Persson</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Elijah Ourth</t>
-        </is>
-      </c>
-      <c r="AY3" t="inlineStr">
-        <is>
-          <t>Ecogain</t>
-        </is>
-      </c>
+          <t>Mimmi Persson</t>
+        </is>
+      </c>
+      <c r="AY3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>121283100</v>
+        <v>121585633</v>
       </c>
       <c r="B4" t="n">
-        <v>92001</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91909</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>4364</v>
+        <v>1202</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -927,10 +922,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>691921</v>
+        <v>691813</v>
       </c>
       <c r="R4" t="n">
-        <v>7138415</v>
+        <v>7138277</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -960,9 +955,19 @@
           <t>2024-08-28</t>
         </is>
       </c>
+      <c r="Z4" t="inlineStr">
+        <is>
+          <t>14:41</t>
+        </is>
+      </c>
       <c r="AA4" t="inlineStr">
         <is>
           <t>2024-08-28</t>
+        </is>
+      </c>
+      <c r="AB4" t="inlineStr">
+        <is>
+          <t>14:41</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -977,12 +982,12 @@
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Elijah Ourth</t>
+          <t>Aron Dynesius</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Elijah Ourth</t>
+          <t>Aron Dynesius</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr">
@@ -993,19 +998,14 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>122031483</v>
+        <v>121283095</v>
       </c>
       <c r="B5" t="n">
-        <v>92082</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93197</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
@@ -1026,24 +1026,20 @@
           <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+      <c r="I5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Byssträsk, Ly lm</t>
+          <t>Vittanliden, Ly lm</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>691930</v>
+        <v>691922</v>
       </c>
       <c r="R5" t="n">
-        <v>7138353</v>
+        <v>7138424</v>
       </c>
       <c r="S5" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1067,17 +1063,12 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2024-11-22</t>
+          <t>2024-08-28</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2024-11-22</t>
-        </is>
-      </c>
-      <c r="AC5" t="inlineStr">
-        <is>
-          <t>Påträffad under Sveaskogs naturvärdesinventering</t>
+          <t>2024-08-28</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1092,31 +1083,30 @@
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Mimmi Persson</t>
+          <t>Elijah Ourth</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Mimmi Persson</t>
-        </is>
-      </c>
-      <c r="AY5" t="inlineStr"/>
+          <t>Elijah Ourth</t>
+        </is>
+      </c>
+      <c r="AY5" t="inlineStr">
+        <is>
+          <t>Ecogain</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>122031256</v>
+        <v>121283100</v>
       </c>
       <c r="B6" t="n">
-        <v>92082</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93197</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
@@ -1137,24 +1127,20 @@
           <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+      <c r="I6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Byssträsk, Ly lm</t>
+          <t>Vittanliden, Ly lm</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>691950</v>
+        <v>691921</v>
       </c>
       <c r="R6" t="n">
-        <v>7138360</v>
+        <v>7138415</v>
       </c>
       <c r="S6" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1178,17 +1164,12 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2024-11-12</t>
+          <t>2024-08-28</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>2024-11-12</t>
-        </is>
-      </c>
-      <c r="AC6" t="inlineStr">
-        <is>
-          <t>Påträffad under Sveaskogs naturvärdesinventering</t>
+          <t>2024-08-28</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1203,49 +1184,48 @@
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Mimmi Persson</t>
+          <t>Elijah Ourth</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Mimmi Persson</t>
-        </is>
-      </c>
-      <c r="AY6" t="inlineStr"/>
+          <t>Elijah Ourth</t>
+        </is>
+      </c>
+      <c r="AY6" t="inlineStr">
+        <is>
+          <t>Ecogain</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>122031257</v>
+        <v>122031256</v>
       </c>
       <c r="B7" t="n">
-        <v>91053</v>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93197</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>65</v>
+        <v>4364</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Fläckporing</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Anthoporia albobrunnea</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Romell) Karasiński &amp; Niemelä</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
@@ -1259,10 +1239,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>691922</v>
+        <v>691950</v>
       </c>
       <c r="R7" t="n">
-        <v>7138420</v>
+        <v>7138360</v>
       </c>
       <c r="S7" t="n">
         <v>5</v>
@@ -1326,37 +1306,32 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>122031430</v>
+        <v>122031483</v>
       </c>
       <c r="B8" t="n">
-        <v>91053</v>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93197</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>65</v>
+        <v>4364</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Fläckporing</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Anthoporia albobrunnea</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Romell) Karasiński &amp; Niemelä</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
@@ -1370,10 +1345,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>691925</v>
+        <v>691930</v>
       </c>
       <c r="R8" t="n">
-        <v>7138401</v>
+        <v>7138353</v>
       </c>
       <c r="S8" t="n">
         <v>5</v>
@@ -1437,57 +1412,48 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>122031768</v>
+        <v>121283098</v>
       </c>
       <c r="B9" t="n">
-        <v>78387</v>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Byssträsk, Ly lm</t>
+          <t>Vittanliden, Ly lm</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>691878</v>
+        <v>691902</v>
       </c>
       <c r="R9" t="n">
-        <v>7138386</v>
+        <v>7138371</v>
       </c>
       <c r="S9" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1511,17 +1477,12 @@
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>2024-11-22</t>
+          <t>2024-08-28</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>2024-11-22</t>
-        </is>
-      </c>
-      <c r="AC9" t="inlineStr">
-        <is>
-          <t>Påträffad under Sveaskogs naturvärdesinventering</t>
+          <t>2024-08-28</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1536,27 +1497,26 @@
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>Mimmi Persson</t>
+          <t>Elijah Ourth</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Mimmi Persson</t>
-        </is>
-      </c>
-      <c r="AY9" t="inlineStr"/>
+          <t>Elijah Ourth</t>
+        </is>
+      </c>
+      <c r="AY9" t="inlineStr">
+        <is>
+          <t>Ecogain</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
         <v>122031255</v>
       </c>
       <c r="B10" t="n">
-        <v>78387</v>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79084</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1656,6 +1616,112 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>122031768</v>
+      </c>
+      <c r="B11" t="n">
+        <v>79084</v>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E11" t="n">
+        <v>6446</v>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Kolflarnlav</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>Carbonicola anthracophila</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="P11" t="inlineStr">
+        <is>
+          <t>Byssträsk, Ly lm</t>
+        </is>
+      </c>
+      <c r="Q11" t="n">
+        <v>691878</v>
+      </c>
+      <c r="R11" t="n">
+        <v>7138386</v>
+      </c>
+      <c r="S11" t="n">
+        <v>5</v>
+      </c>
+      <c r="T11" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U11" t="inlineStr">
+        <is>
+          <t>Lycksele</t>
+        </is>
+      </c>
+      <c r="V11" t="inlineStr">
+        <is>
+          <t>Lycksele lappmark</t>
+        </is>
+      </c>
+      <c r="W11" t="inlineStr">
+        <is>
+          <t>Lycksele</t>
+        </is>
+      </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>2024-11-22</t>
+        </is>
+      </c>
+      <c r="AA11" t="inlineStr">
+        <is>
+          <t>2024-11-22</t>
+        </is>
+      </c>
+      <c r="AC11" t="inlineStr">
+        <is>
+          <t>Påträffad under Sveaskogs naturvärdesinventering</t>
+        </is>
+      </c>
+      <c r="AD11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT11" t="inlineStr"/>
+      <c r="AW11" t="inlineStr">
+        <is>
+          <t>Mimmi Persson</t>
+        </is>
+      </c>
+      <c r="AX11" t="inlineStr">
+        <is>
+          <t>Mimmi Persson</t>
+        </is>
+      </c>
+      <c r="AY11" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 54905-2024 artfynd.xlsx
+++ b/artfynd/A 54905-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY11"/>
+  <dimension ref="A1:AZ11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -783,6 +788,11 @@
           <t>Ecogain</t>
         </is>
       </c>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121585633</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -889,6 +899,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122031257</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -995,6 +1010,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122031430</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1096,6 +1116,11 @@
           <t>Ecogain</t>
         </is>
       </c>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121283095</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1197,6 +1222,11 @@
           <t>Ecogain</t>
         </is>
       </c>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121283100</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1303,6 +1333,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122031256</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1409,6 +1444,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122031483</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1510,6 +1550,11 @@
           <t>Ecogain</t>
         </is>
       </c>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121283098</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1616,6 +1661,11 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122031255</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1722,8 +1772,25 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122031768</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>